--- a/artfynd/A 20886-2026 artfynd.xlsx
+++ b/artfynd/A 20886-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62055447</v>
+        <v>62055685</v>
       </c>
       <c r="B2" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479070.2729963824</v>
+        <v>478874</v>
       </c>
       <c r="R2" t="n">
-        <v>7028813.739359171</v>
+        <v>7028916</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2002-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-08-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Mellan Äsmyrens östspets och Bötelsmyren, ca 2,1 km nordväst om Nävrans utlopp i Långan,</t>
+          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Söder om Bötelsmyrens sydvästra flank, ca 2,3 km nordväst om Nävrans utlopp i Långan,</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +764,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,57 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79394618</v>
+        <v>62055709</v>
       </c>
       <c r="B3" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bötelsmyren, S om vid Nävran, Jmt</t>
+          <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479362.1069162663</v>
+        <v>478874</v>
       </c>
       <c r="R3" t="n">
-        <v>7028742.345097388</v>
+        <v>7028916</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Söder om Bötelsmyrens sydvästra flank, ca 2,3 km nordväst om Nävrans utlopp i Långan,</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,18 +878,249 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Granlåga med ullticka</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Granlåga med ullticka</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>79394618</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bötelsmyren, S om vid Nävran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>479362</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7028742</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-08-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-08-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Staffan Åström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Staffan Åström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>62055447</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>479070</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7028814</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Mellan Äsmyrens östspets och Bötelsmyren, ca 2,1 km nordväst om Nävrans utlopp i Långan,</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20886-2026 artfynd.xlsx
+++ b/artfynd/A 20886-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055685</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055709</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79394618</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,8 +1141,19 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055447</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>